--- a/data/trans_orig/P79_n_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P79_n_R2-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>37430</t>
+          <t>42868</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27678</t>
+          <t>31952</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49250</t>
+          <t>56036</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>50120</t>
+          <t>57516</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40414</t>
+          <t>46396</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61035</t>
+          <t>68692</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>87550</t>
+          <t>100384</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71501</t>
+          <t>85834</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104394</t>
+          <t>118086</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>477508</t>
+          <t>535661</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>465688</t>
+          <t>522493</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>487260</t>
+          <t>546577</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>705388</t>
+          <t>764522</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>694473</t>
+          <t>753346</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>715094</t>
+          <t>775642</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1182896</t>
+          <t>1300183</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1166052</t>
+          <t>1282481</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1198945</t>
+          <t>1314733</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>93,87%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>81100</t>
+          <t>94442</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54510</t>
+          <t>74678</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>105271</t>
+          <t>119722</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>73632</t>
+          <t>85108</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52745</t>
+          <t>68393</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98255</t>
+          <t>108642</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>154733</t>
+          <t>179550</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>118829</t>
+          <t>151894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>188953</t>
+          <t>209709</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2209227</t>
+          <t>2136124</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2185056</t>
+          <t>2110844</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2235817</t>
+          <t>2155888</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2164191</t>
+          <t>2086284</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2139568</t>
+          <t>2062750</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2185078</t>
+          <t>2102999</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4373417</t>
+          <t>4222409</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4339197</t>
+          <t>4192250</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4409321</t>
+          <t>4250065</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,67 +1411,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15528</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>8570</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4182</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14738</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6592</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3179</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12007</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14157</t>
+          <t>17942</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>11135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22810</t>
+          <t>26978</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1524,67 +1524,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>639058</t>
+          <t>702215</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>631095</t>
+          <t>694229</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>643236</t>
+          <t>707968</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>98,68%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>726307</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>720139</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>730695</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>98,83%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,6%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>993</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>653871</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>648456</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>657284</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,0%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1292929</t>
+          <t>1428522</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1284276</t>
+          <t>1419486</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1298657</t>
+          <t>1435329</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>126095</t>
+          <t>146683</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98670</t>
+          <t>122096</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>155325</t>
+          <t>173986</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>130345</t>
+          <t>151194</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105257</t>
+          <t>127512</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>156520</t>
+          <t>175763</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>256440</t>
+          <t>297877</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>217278</t>
+          <t>265589</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>292747</t>
+          <t>335344</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3325794</t>
+          <t>3374000</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3296564</t>
+          <t>3346697</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3353219</t>
+          <t>3398587</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3523449</t>
+          <t>3577113</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3497274</t>
+          <t>3552544</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3548537</t>
+          <t>3600795</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6849243</t>
+          <t>6951113</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6812936</t>
+          <t>6913646</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6888405</t>
+          <t>6983401</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
